--- a/DATA/04_operating_metrics.xlsx
+++ b/DATA/04_operating_metrics.xlsx
@@ -2849,6 +2849,12 @@
       <c r="C57">
         <v>2021</v>
       </c>
+      <c r="D57">
+        <v>135</v>
+      </c>
+      <c r="E57">
+        <v>2166</v>
+      </c>
       <c r="F57">
         <v>148</v>
       </c>
